--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_individual_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_individual_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008566648607316726</v>
       </c>
       <c r="C2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>50957127</v>
+        <v>3704727</v>
       </c>
       <c r="L2" t="n">
-        <v>26807257</v>
+        <v>1692657</v>
       </c>
       <c r="M2" t="n">
-        <v>6158987</v>
+        <v>326416</v>
       </c>
       <c r="N2" t="n">
-        <v>176958</v>
+        <v>7660</v>
       </c>
       <c r="O2" t="n">
-        <v>3785259</v>
+        <v>207288</v>
       </c>
       <c r="P2" t="n">
-        <v>1305722</v>
+        <v>27970</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999390840530396</v>
+        <v>0.9999397993087769</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8246269822120667</v>
+        <v>0.7180229425430298</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6799819469451904</v>
+        <v>0.5111986398696899</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5956889986991882</v>
+        <v>0.3818820714950562</v>
       </c>
       <c r="U2" t="n">
-        <v>0.186789482831955</v>
+        <v>0.05601298809051514</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6319896578788757</v>
+        <v>0.4092015326023102</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7675525546073914</v>
+        <v>0.590208888053894</v>
       </c>
       <c r="X2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="AG2" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AH2" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AI2" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9556694626808167</v>
+        <v>0.9541478753089905</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118999242782593</v>
+        <v>0.9129630327224731</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581674098968506</v>
+        <v>0.8576433062553406</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615565419197083</v>
+        <v>0.6601934432983398</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019808769226074</v>
+        <v>0.9016708135604858</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002053537536211935</v>
       </c>
       <c r="C3" t="n">
-        <v>4347</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>50957127</v>
+        <v>3704727</v>
       </c>
       <c r="E3" t="n">
-        <v>8579410</v>
+        <v>1135168</v>
       </c>
       <c r="F3" t="n">
-        <v>344827</v>
+        <v>72767</v>
       </c>
       <c r="G3" t="n">
-        <v>24528</v>
+        <v>6723</v>
       </c>
       <c r="H3" t="n">
-        <v>35892</v>
+        <v>8583</v>
       </c>
       <c r="I3" t="n">
-        <v>2075</v>
+        <v>180</v>
       </c>
       <c r="J3" t="n">
-        <v>120194849</v>
+        <v>10016242</v>
       </c>
       <c r="K3" t="n">
-        <v>125169968</v>
+        <v>9946195</v>
       </c>
       <c r="L3" t="n">
-        <v>143851672</v>
+        <v>11365636</v>
       </c>
       <c r="M3" t="n">
-        <v>180533081</v>
+        <v>14855729</v>
       </c>
       <c r="N3" t="n">
-        <v>194111199</v>
+        <v>16110437</v>
       </c>
       <c r="O3" t="n">
-        <v>187625100</v>
+        <v>15517327</v>
       </c>
       <c r="P3" t="n">
-        <v>193237177</v>
+        <v>16116130</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8500192165374756</v>
+        <v>0.7516931295394897</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6788829565048218</v>
+        <v>0.5059552192687988</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5478628873825073</v>
+        <v>0.345219761133194</v>
       </c>
       <c r="U3" t="n">
-        <v>0.164827823638916</v>
+        <v>0.08504591137170792</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6179079413414001</v>
+        <v>0.4040749073028564</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5621823668479919</v>
+        <v>0.1441381126642227</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="Z3" t="n">
-        <v>2363094</v>
+        <v>195844</v>
       </c>
       <c r="AA3" t="n">
-        <v>101765</v>
+        <v>8538</v>
       </c>
       <c r="AB3" t="n">
-        <v>81730</v>
+        <v>6822</v>
       </c>
       <c r="AC3" t="n">
-        <v>302</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120199464</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>133344343</v>
+        <v>11174399</v>
       </c>
       <c r="AG3" t="n">
-        <v>152997368</v>
+        <v>12694080</v>
       </c>
       <c r="AH3" t="n">
-        <v>183120991</v>
+        <v>15249719</v>
       </c>
       <c r="AI3" t="n">
-        <v>194518645</v>
+        <v>16208962</v>
       </c>
       <c r="AJ3" t="n">
-        <v>189229252</v>
+        <v>15766212</v>
       </c>
       <c r="AK3" t="n">
-        <v>193473427</v>
+        <v>16122228</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575091600418091</v>
+        <v>0.9571381807327271</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097229242324829</v>
+        <v>0.9094282388687134</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570423722267151</v>
+        <v>0.8560332655906677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6608491539955139</v>
+        <v>0.6593944430351257</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013246297836304</v>
+        <v>0.900807797908783</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>9958532</v>
+        <v>1292433</v>
       </c>
       <c r="E4" t="n">
-        <v>26807257</v>
+        <v>1692657</v>
       </c>
       <c r="F4" t="n">
-        <v>2239342</v>
+        <v>273722</v>
       </c>
       <c r="G4" t="n">
-        <v>115801</v>
+        <v>28702</v>
       </c>
       <c r="H4" t="n">
-        <v>334435</v>
+        <v>55679</v>
       </c>
       <c r="I4" t="n">
-        <v>31936</v>
+        <v>2275</v>
       </c>
       <c r="J4" t="n">
-        <v>4615</v>
+        <v>380</v>
       </c>
       <c r="K4" t="n">
-        <v>10837026</v>
+        <v>1454895</v>
       </c>
       <c r="L4" t="n">
-        <v>12616225</v>
+        <v>1618496</v>
       </c>
       <c r="M4" t="n">
-        <v>4180279</v>
+        <v>528340</v>
       </c>
       <c r="N4" t="n">
-        <v>770408</v>
+        <v>129094</v>
       </c>
       <c r="O4" t="n">
-        <v>2204173</v>
+        <v>299279</v>
       </c>
       <c r="P4" t="n">
-        <v>395428</v>
+        <v>19420</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999695420265198</v>
+        <v>0.9999698996543884</v>
       </c>
       <c r="R4" t="n">
-        <v>0.837130606174469</v>
+        <v>0.734472393989563</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6794320344924927</v>
+        <v>0.5085633993148804</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5707758665084839</v>
+        <v>0.3626266419887543</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1751227974891663</v>
+        <v>0.06754165887832642</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6248694658279419</v>
+        <v>0.4066220819950104</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6490083336830139</v>
+        <v>0.2316931784152985</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2487043</v>
+        <v>211876</v>
       </c>
       <c r="Z4" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AA4" t="n">
-        <v>996591</v>
+        <v>84107</v>
       </c>
       <c r="AB4" t="n">
-        <v>66559</v>
+        <v>5676</v>
       </c>
       <c r="AC4" t="n">
-        <v>13785</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2662651</v>
+        <v>226691</v>
       </c>
       <c r="AG4" t="n">
-        <v>3470529</v>
+        <v>290052</v>
       </c>
       <c r="AH4" t="n">
-        <v>1592369</v>
+        <v>134350</v>
       </c>
       <c r="AI4" t="n">
-        <v>362962</v>
+        <v>30569</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600021</v>
+        <v>50394</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565883874893188</v>
+        <v>0.9556406140327454</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910810112953186</v>
+        <v>0.9111921787261963</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576045632362366</v>
+        <v>0.8568375706672668</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612026691436768</v>
+        <v>0.6597936749458313</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016525745391846</v>
+        <v>0.9012390971183777</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>627844</v>
+        <v>119602</v>
       </c>
       <c r="E5" t="n">
-        <v>3235977</v>
+        <v>349601</v>
       </c>
       <c r="F5" t="n">
-        <v>6158987</v>
+        <v>326416</v>
       </c>
       <c r="G5" t="n">
-        <v>234714</v>
+        <v>37584</v>
       </c>
       <c r="H5" t="n">
-        <v>890312</v>
+        <v>105616</v>
       </c>
       <c r="I5" t="n">
-        <v>94006</v>
+        <v>6712</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8991079</v>
+        <v>1223783</v>
       </c>
       <c r="L5" t="n">
-        <v>12680046</v>
+        <v>1652811</v>
       </c>
       <c r="M5" t="n">
-        <v>5082853</v>
+        <v>619115</v>
       </c>
       <c r="N5" t="n">
-        <v>896635</v>
+        <v>82409</v>
       </c>
       <c r="O5" t="n">
-        <v>2340668</v>
+        <v>305706</v>
       </c>
       <c r="P5" t="n">
-        <v>1016873</v>
+        <v>166080</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999764561653137</v>
+        <v>0.9999767541885376</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8988130688667297</v>
+        <v>0.8359618186950684</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8709079027175903</v>
+        <v>0.7996701002120972</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9527283310890198</v>
+        <v>0.9297316074371338</v>
       </c>
       <c r="U5" t="n">
-        <v>0.991492748260498</v>
+        <v>0.9870478510856628</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9768067598342896</v>
+        <v>0.96295166015625</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9927927255630493</v>
+        <v>0.9886402487754822</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>96751</v>
+        <v>8160</v>
       </c>
       <c r="Z5" t="n">
-        <v>1032439</v>
+        <v>87923</v>
       </c>
       <c r="AA5" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AB5" t="n">
-        <v>119853</v>
+        <v>10057</v>
       </c>
       <c r="AC5" t="n">
-        <v>350460</v>
+        <v>29344</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2547251</v>
+        <v>211245</v>
       </c>
       <c r="AG5" t="n">
-        <v>3564799</v>
+        <v>303005</v>
       </c>
       <c r="AH5" t="n">
-        <v>1607107</v>
+        <v>136125</v>
       </c>
       <c r="AI5" t="n">
-        <v>364110</v>
+        <v>30678</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604478</v>
+        <v>50885</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973412811756134</v>
+        <v>0.9731814861297607</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964097261428833</v>
+        <v>0.9636821150779724</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836724400520325</v>
+        <v>0.9834365248680115</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962896108627319</v>
+        <v>0.9962493181228638</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938532114028931</v>
+        <v>0.9937978386878967</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983713626861572</v>
+        <v>0.9983611106872559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>180942</v>
+        <v>20972</v>
       </c>
       <c r="E6" t="n">
-        <v>260962</v>
+        <v>27030</v>
       </c>
       <c r="F6" t="n">
-        <v>317357</v>
+        <v>22845</v>
       </c>
       <c r="G6" t="n">
-        <v>176958</v>
+        <v>7660</v>
       </c>
       <c r="H6" t="n">
-        <v>125883</v>
+        <v>11036</v>
       </c>
       <c r="I6" t="n">
-        <v>11244</v>
+        <v>508</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78306</v>
+        <v>6619</v>
       </c>
       <c r="Z6" t="n">
-        <v>64303</v>
+        <v>5393</v>
       </c>
       <c r="AA6" t="n">
-        <v>131730</v>
+        <v>11143</v>
       </c>
       <c r="AB6" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AC6" t="n">
-        <v>83993</v>
+        <v>7037</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>65092</v>
+        <v>19866</v>
       </c>
       <c r="E7" t="n">
-        <v>488039</v>
+        <v>94089</v>
       </c>
       <c r="F7" t="n">
-        <v>1168919</v>
+        <v>135519</v>
       </c>
       <c r="G7" t="n">
-        <v>362451</v>
+        <v>46487</v>
       </c>
       <c r="H7" t="n">
-        <v>3785259</v>
+        <v>207288</v>
       </c>
       <c r="I7" t="n">
-        <v>256167</v>
+        <v>9745</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>215</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9720</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358302</v>
+        <v>30228</v>
       </c>
       <c r="AB7" t="n">
-        <v>91626</v>
+        <v>7747</v>
       </c>
       <c r="AC7" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4616</v>
+        <v>2022</v>
       </c>
       <c r="E8" t="n">
-        <v>51837</v>
+        <v>12608</v>
       </c>
       <c r="F8" t="n">
-        <v>109834</v>
+        <v>23487</v>
       </c>
       <c r="G8" t="n">
-        <v>32914</v>
+        <v>9598</v>
       </c>
       <c r="H8" t="n">
-        <v>817651</v>
+        <v>118365</v>
       </c>
       <c r="I8" t="n">
-        <v>1305722</v>
+        <v>27970</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
